--- a/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20241.xlsx
+++ b/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20241.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="23">
   <si>
     <t>Mat</t>
   </si>
@@ -77,6 +77,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>FERRER</t>
+  </si>
+  <si>
+    <t>VANESA</t>
   </si>
 </sst>
 </file>
@@ -620,16 +629,19 @@
         <v>35</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>35</v>
       </c>
-      <c r="E2">
-        <v>35</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>8.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -643,16 +655,19 @@
         <v>21</v>
       </c>
       <c r="D3">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>95.23999999999999</v>
+      </c>
+      <c r="H3">
+        <v>6.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -666,16 +681,19 @@
         <v>40</v>
       </c>
       <c r="D4">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>7.3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -689,16 +707,19 @@
         <v>40</v>
       </c>
       <c r="D5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -754,16 +775,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>97.14</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>8.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -789,7 +810,7 @@
         <v>95.23999999999999</v>
       </c>
       <c r="H3">
-        <v>6.3</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -815,7 +836,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -841,7 +862,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -851,7 +872,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -881,6 +902,29 @@
         <v>19</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>23330051920237</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20241.xlsx
+++ b/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20241.xlsx
@@ -922,7 +922,7 @@
         <v>12</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20241.xlsx
+++ b/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20241.xlsx
@@ -79,13 +79,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>FERRER</t>
-  </si>
-  <si>
-    <t>VANESA</t>
+    <t>VERA</t>
+  </si>
+  <si>
+    <t>VALERIO</t>
+  </si>
+  <si>
+    <t>OSCAR ALEXANDER</t>
   </si>
 </sst>
 </file>
@@ -535,7 +535,7 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -544,13 +544,13 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G4">
         <v>100</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -561,7 +561,7 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -570,13 +570,13 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G5">
         <v>100</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -678,7 +678,7 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -687,13 +687,13 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G4">
         <v>100</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -704,7 +704,7 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -713,13 +713,13 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G5">
         <v>100</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
     </row>
   </sheetData>
@@ -784,7 +784,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -810,7 +810,7 @@
         <v>95.23999999999999</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -821,7 +821,7 @@
         <v>13</v>
       </c>
       <c r="C4">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -830,13 +830,13 @@
         <v>0</v>
       </c>
       <c r="F4">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G4">
         <v>100</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -847,7 +847,7 @@
         <v>13</v>
       </c>
       <c r="C5">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -856,13 +856,13 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G5">
         <v>100</v>
       </c>
       <c r="H5">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -904,7 +904,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920237</v>
+        <v>23330051920278</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
@@ -922,7 +922,7 @@
         <v>12</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20241.xlsx
+++ b/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20241.xlsx
@@ -922,7 +922,7 @@
         <v>12</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
